--- a/countries/se-t/2026-2029.xlsx
+++ b/countries/se-t/2026-2029.xlsx
@@ -64633,10 +64633,10 @@
         </is>
       </c>
       <c r="N455" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O455" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U455" t="inlineStr">
         <is>
@@ -65590,7 +65590,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1380</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="16">
